--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486670_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486670_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.7447</v>
+        <v>7.6471</v>
       </c>
       <c r="E2" t="n">
-        <v>8.391299999999999</v>
+        <v>6.84</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3534</v>
+        <v>0.8071</v>
       </c>
       <c r="G2" t="n">
         <v>1.6512</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8079</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9302</v>
+        <v>0.3789</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8777</v>
+        <v>0.3314</v>
       </c>
       <c r="V2" t="n">
         <v>3.3548</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>A. LOPEZ ROMERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8762</v>
+        <v>4.5065</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8468</v>
+        <v>4.666</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9706</v>
+        <v>-0.1594</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2394</v>
+        <v>4.7479</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2417</v>
+        <v>0.4685</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0023</v>
+        <v>4.2794</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7092</v>
+        <v>6.2453</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2766</v>
+        <v>1.1588</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5674</v>
+        <v>5.0865</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4698</v>
+        <v>-1.4973</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0349</v>
+        <v>-0.6903</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5651</v>
+        <v>-0.8071</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q3" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.1585</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.4345</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.6139</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>0.9654</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.2852</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.9099</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.3754</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-0.6138</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. LOPEZ ROMERA</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0748</v>
+        <v>4.4598</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5073</v>
+        <v>5.2814</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4326</v>
+        <v>-0.8216</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7479</v>
+        <v>3.2394</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4685</v>
+        <v>3.2417</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2794</v>
+        <v>-0.0023</v>
       </c>
       <c r="J4" t="n">
-        <v>6.2453</v>
+        <v>3.7092</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1588</v>
+        <v>4.2766</v>
       </c>
       <c r="L4" t="n">
-        <v>5.0865</v>
+        <v>-0.5674</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4973</v>
+        <v>-0.4698</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6903</v>
+        <v>-1.0349</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8071</v>
+        <v>0.5651</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8662</v>
+        <v>0.8689</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7725</v>
+        <v>0.3445</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.09370000000000001</v>
+        <v>0.5243</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.494</v>
+        <v>3.574</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4927</v>
+        <v>3.5479</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0012</v>
+        <v>0.0261</v>
       </c>
       <c r="G5" t="n">
         <v>1.9745</v>
@@ -844,13 +844,13 @@
         <v>2.7031</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0441</v>
+        <v>0.1241</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3866</v>
+        <v>-0.3314</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4307</v>
+        <v>0.4555</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2277</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9613</v>
+        <v>3.219</v>
       </c>
       <c r="E6" t="n">
-        <v>2.986</v>
+        <v>3.7651</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0247</v>
+        <v>-0.5462</v>
       </c>
       <c r="G6" t="n">
         <v>5.5349</v>
@@ -922,13 +922,13 @@
         <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8665</v>
+        <v>1.1241</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5795</v>
+        <v>0.1997</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4459</v>
+        <v>0.9245</v>
       </c>
       <c r="V6" t="n">
         <v>-3.4401</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4712</v>
+        <v>0.5457</v>
       </c>
       <c r="E7" t="n">
         <v>-0.7038</v>
       </c>
       <c r="F7" t="n">
-        <v>1.175</v>
+        <v>1.2495</v>
       </c>
       <c r="G7" t="n">
         <v>1.5579</v>
@@ -1000,13 +1000,13 @@
         <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0055</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V7" t="n">
         <v>0.6565</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. QUIJADA GARCÍA</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1267</v>
+        <v>-1.1198</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2666</v>
+        <v>-1.5807</v>
       </c>
       <c r="F8" t="n">
-        <v>0.14</v>
+        <v>0.4609</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2495</v>
+        <v>0.1079</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.2968</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3458</v>
+        <v>0.4047</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9798</v>
+        <v>0.309</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2136</v>
+        <v>1.1521</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7663</v>
+        <v>-0.8431</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2697</v>
+        <v>-0.2011</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6901</v>
+        <v>-1.4489</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4205</v>
+        <v>1.2478</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3862</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5792</v>
+        <v>1.7377</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.491</v>
+        <v>0.193</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.607</v>
+        <v>0.0411</v>
       </c>
       <c r="U8" t="n">
-        <v>0.116</v>
+        <v>0.152</v>
       </c>
       <c r="V8" t="n">
+        <v>-1.2277</v>
+      </c>
+      <c r="W8" t="n">
         <v>0</v>
       </c>
-      <c r="W8" t="n">
-        <v>0.2856</v>
-      </c>
       <c r="X8" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>E. QUIJADA GARCÍA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1625</v>
+        <v>-1.484</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2012</v>
+        <v>-1.7978</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0388</v>
+        <v>0.3138</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1079</v>
+        <v>-1.2495</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2968</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4047</v>
+        <v>-0.3458</v>
       </c>
       <c r="J9" t="n">
-        <v>0.309</v>
+        <v>-0.9798</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1521</v>
+        <v>-0.2136</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8431</v>
+        <v>-0.7663</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2011</v>
+        <v>-0.2697</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4489</v>
+        <v>-0.6901</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2478</v>
+        <v>0.4205</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1931</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7377</v>
+        <v>0.5792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8496</v>
+        <v>0.1517</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5795</v>
+        <v>-0.1381</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2702</v>
+        <v>0.2898</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0778</v>
+        <v>-2.8172</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4339</v>
+        <v>-2.1236</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6439</v>
+        <v>-0.6936</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2823</v>
@@ -1234,13 +1234,13 @@
         <v>2.1239</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6949</v>
+        <v>-0.4343</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5243</v>
+        <v>-0.214</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1706</v>
+        <v>-0.2203</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3282</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.7474</v>
+        <v>15.0233</v>
       </c>
       <c r="E12" t="n">
-        <v>15.0206</v>
+        <v>15.2965</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2733000000000001</v>
+        <v>-0.2733</v>
       </c>
       <c r="G12" t="n">
         <v>13.6557</v>
@@ -1369,10 +1369,10 @@
         <v>16.2125</v>
       </c>
       <c r="L12" t="n">
-        <v>4.555699999999999</v>
+        <v>4.5557</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.112400000000001</v>
+        <v>-7.112399999999999</v>
       </c>
       <c r="N12" t="n">
         <v>-9.3161</v>
@@ -1381,7 +1381,7 @@
         <v>2.2037</v>
       </c>
       <c r="P12" t="n">
-        <v>3.861600000000001</v>
+        <v>3.8616</v>
       </c>
       <c r="Q12" t="n">
         <v>-10.6194</v>
@@ -1390,10 +1390,10 @@
         <v>14.481</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2415</v>
+        <v>1.5172</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3819</v>
+        <v>-1.1058</v>
       </c>
       <c r="U12" t="n">
         <v>2.6232</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.207700000000001</v>
+        <v>10.2641</v>
       </c>
       <c r="E13" t="n">
-        <v>12.0039</v>
+        <v>12.6244</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7962</v>
+        <v>-2.3603</v>
       </c>
       <c r="G13" t="n">
         <v>4.0773</v>
@@ -1468,13 +1468,13 @@
         <v>2.1239</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4288</v>
+        <v>-0.3724</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1313</v>
+        <v>-0.5108</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2975</v>
+        <v>0.1384</v>
       </c>
       <c r="V13" t="n">
         <v>6.7523</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0525</v>
+        <v>-0.5366</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0917</v>
+        <v>-1.402</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0392</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6771</v>
@@ -1546,13 +1546,13 @@
         <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4083</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.11</v>
+        <v>-0.2003</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2983</v>
+        <v>0.1245</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9421</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7816</v>
+        <v>-1.2161</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8192</v>
+        <v>1.509</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.6009</v>
+        <v>-2.725</v>
       </c>
       <c r="G15" t="n">
         <v>-0.416</v>
@@ -1624,13 +1624,13 @@
         <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4413</v>
+        <v>0.0069</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0548</v>
+        <v>-0.2554</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3865</v>
+        <v>0.2623</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6138</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Y. BOUBACAR</t>
+          <t>E. RAMÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7836</v>
+        <v>-3.1176</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0777</v>
+        <v>-1.0735</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.706</v>
+        <v>-2.0441</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.6911</v>
+        <v>-2.5674</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.7099</v>
+        <v>-1.3104</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9812</v>
+        <v>-1.257</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.214</v>
+        <v>0.0822</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2954</v>
+        <v>0.6903</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0814</v>
+        <v>-0.6081</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.4771</v>
+        <v>-2.6495</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.4145</v>
+        <v>-2.0007</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0626</v>
+        <v>-0.6489</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.3169</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3169</v>
+        <v>-0.0482</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2682</v>
+        <v>-0.352</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0487</v>
+        <v>0.3038</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5559</v>
+        <v>0.6565</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1851</v>
+        <v>1.5133</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3709</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. RAMÓN FERNÁNDEZ</t>
+          <t>Y. BOUBACAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.0528</v>
+        <v>-3.3145</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9701</v>
+        <v>-2.1119</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0827</v>
+        <v>-1.2026</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5674</v>
+        <v>-4.6911</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3104</v>
+        <v>-3.7099</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.257</v>
+        <v>-0.9812</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0822</v>
+        <v>-1.214</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6903</v>
+        <v>-1.2954</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6081</v>
+        <v>0.0814</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6495</v>
+        <v>-3.4771</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0007</v>
+        <v>-2.4145</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6489</v>
+        <v>-1.0626</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.3169</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0166</v>
+        <v>0.7861</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2486</v>
+        <v>0.234</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2652</v>
+        <v>0.5521</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6565</v>
+        <v>1.5559</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5133</v>
+        <v>1.1851</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8568</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>F. QUERO CARMONA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.4308</v>
+        <v>-3.9205</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.0022</v>
+        <v>0.081</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4286</v>
+        <v>-4.0015</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9605</v>
+        <v>-2.461</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9657</v>
+        <v>-2.9652</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9947</v>
+        <v>0.5041</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4699</v>
+        <v>1.4922</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1382</v>
+        <v>-0.3436</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6081</v>
+        <v>1.8357</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4906</v>
+        <v>-3.9532</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1039</v>
+        <v>-2.6216</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3866</v>
+        <v>-1.3316</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1585</v>
+        <v>-1.3515</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6288</v>
+        <v>0.0964</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7174</v>
+        <v>-0.3452</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0885</v>
+        <v>0.4416</v>
       </c>
       <c r="V18" t="n">
+        <v>-1.5559</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="X18" t="n">
         <v>-1.8415</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-0.6565</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.1851</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. QUERO CARMONA</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.0266</v>
+        <v>-3.933</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5395</v>
+        <v>-2.6919</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.4871</v>
+        <v>-1.2411</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.461</v>
+        <v>-1.9605</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.9652</v>
+        <v>-0.9657</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5041</v>
+        <v>-0.9947</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4922</v>
+        <v>-0.4699</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3436</v>
+        <v>0.1382</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8357</v>
+        <v>-0.6081</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.9532</v>
+        <v>-1.4906</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.6216</v>
+        <v>-1.1039</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3316</v>
+        <v>-0.3866</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3515</v>
+        <v>-1.1585</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0097</v>
+        <v>-0.131</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9657</v>
+        <v>-0.4071</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0439</v>
+        <v>0.2761</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5559</v>
+        <v>-1.8415</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2856</v>
+        <v>-0.6565</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8415</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.8271</v>
+        <v>-8.283799999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.8687</v>
+        <v>-6.6619</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9584</v>
+        <v>-1.6219</v>
       </c>
       <c r="G20" t="n">
         <v>-4.96</v>
@@ -2014,13 +2014,13 @@
         <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3571</v>
+        <v>-0.8137</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9933</v>
+        <v>-0.7864</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3638</v>
+        <v>-0.0273</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,28 +2047,28 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-14.7473</v>
+        <v>-14.058</v>
       </c>
       <c r="E21" t="n">
         <v>0.273200000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-15.0207</v>
+        <v>-14.3311</v>
       </c>
       <c r="G21" t="n">
         <v>-13.6558</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.896299999999999</v>
+        <v>-6.8963</v>
       </c>
       <c r="I21" t="n">
-        <v>-6.759500000000001</v>
+        <v>-6.759499999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>7.112499999999999</v>
+        <v>7.1125</v>
       </c>
       <c r="K21" t="n">
-        <v>9.3161</v>
+        <v>9.316099999999999</v>
       </c>
       <c r="L21" t="n">
         <v>-2.2037</v>
@@ -2092,13 +2092,13 @@
         <v>10.6193</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2413</v>
+        <v>-0.5517</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.6233</v>
+        <v>-2.6232</v>
       </c>
       <c r="U21" t="n">
-        <v>1.382</v>
+        <v>2.0715</v>
       </c>
       <c r="V21" t="n">
         <v>4.0114</v>
@@ -2107,7 +2107,7 @@
         <v>10.2648</v>
       </c>
       <c r="X21" t="n">
-        <v>-6.2535</v>
+        <v>-6.253500000000001</v>
       </c>
     </row>
   </sheetData>
